--- a/7_Data_Extraction/Data_Extraction_Luigi.xlsx
+++ b/7_Data_Extraction/Data_Extraction_Luigi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://communitystudentiunina.sharepoint.com/sites/PRINMEDITATE/Shared Documents/SLR/RegressionTestingOptimizationSLR/7_Data_Extraction/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/7_Data_Extraction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="13_ncr:1_{06CFF3AA-4509-1541-B84B-9FA40FAED757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703A5BF8-E5CB-6A4A-9434-75709789D002}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB20CA17-36EF-0C40-AE2D-B7ECCD965C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1720" yWindow="2600" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="294">
   <si>
     <t>ID</t>
   </si>
@@ -138,19 +138,6 @@
   </si>
   <si>
     <t>RQ3.2</t>
-  </si>
-  <si>
-    <t>A Choudhary, AP Agrawal, A Kaur</t>
-  </si>
-  <si>
-    <t>Proceedings of the 11th International Workshop on Search-Based Software Testing, 2018</t>
-  </si>
-  <si>
-    <t>An effective approach for regression test case selection using pareto based multi-objective harmony search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Regression testing is a way of catching bugs in new builds and releases to avoid the product risks. Corrective, progressive, retest all and selective regression testing are strategies to perform regression testing. Retesting all existing test cases is one of the most reliable approaches but it is costly in terms of time and effort. This limitation opened a scope to optimize regression testing cost by selecting only a subset of test cases that can detect faults in optimal time and effort. This paper proposes Pareto based Multi-Objective Harmony Search approach for regression test case selection from an existing test suite to achieve some test adequacy criteria. Fault coverage, unique faults covered and algorithm execution time are utilised as performance measures to achieve optimization criteria. The performance evaluation of proposed approach is performed against Bat Search and Cuckoo Search optimization. The results of statistical tests indicate significant improvement over existing approaches.</t>
   </si>
   <si>
     <t>PS</t>
@@ -281,33 +268,6 @@
   </si>
   <si>
     <t>Regression testing aims to ensure the quality of a software after modification. However, re-executing the entire test suite in regression testing is a time-consuming, costly, and tedious process that often requires additional budget and time. Thus, limited resources always result in early termination and poor quality software. Test case prioritization aims to improve regression testing by re-scheduling the test cases in a manner that could increase the fault detection rate. Risk-based testing has gained popularity in the area of software testing. However, most of the existing methods compute risk values manually, which makes these methods tiresome, laborious, and slow. In this paper, we propose a semi-automatic risk-based test case prioritization approach based on software modification information and methods (functions) invocation relationship. The objective of this research is to make risk-based testing more systematic and flexible by automating the risk assessment process, and find high-risk faults early. The proposed approach utilizes the requirements modification information, complexity, and size of the methods as the risk indicating factors. We applied an automated procedure to extract these risk factors and compute the risk values of the system methods. The proposed approach is empirically evaluated with two software applications with multiple versions in terms of its fault detection rate, both overall and in risky modules. The experimental results suggest that our proposed approach improves test efficiency by spotting defects early overall and even earlier in the high-risk modules than existing state-of-the-art approaches.</t>
-  </si>
-  <si>
-    <t>Jianlei Chia, Yu Quc, Qinghua Zhenga, Zijiang Yangb, Wuxia Jina, Di Cuia, Ting Liua</t>
-  </si>
-  <si>
-    <t>The Journal of Systems and Software</t>
-  </si>
-  <si>
-    <t>Relation-based test case prioritization for regression testing</t>
-  </si>
-  <si>
-    <t>Test case prioritization (TCP), which aims at detecting faults as early as possible is broadly used in pro-
-gram regression testing. Most existing TCP techniques exploit coverage information with the hypothesis
-that higher coverage has more chance to catch bugs. Static structure information such as function and
-statement are frequently employed as coverage granularity. However, the former consumes less costs but
-presents lower capability to detect faults, the latter typically incurs more overhead.
-In this paper, dynamic function call sequences are argued that can guide TCP effectively. Same set of func-
-tions/statements can exhibit very different execution behaviors. Therefore, mapping program behaviors
-to unit-based (function/statement) coverage may not be enough to predict fault detection capability. We
-propose a new approach AGC (Additional Greedy method Call sequence). Our approach leverages dynamic
-relation-based coverage as measurement to extend the original additional greedy coverage algorithm in
-TCP techniques.
-We conduct our experiments on eight real-world java open source projects and systematically compare
-AGC against 22 state-of-the-art TCP techniques with different granularities. Results show that AGC out-
-performs existing techniques on large programs in terms of bug detection capability, and also achieves
-the highest mean APFD value. The performance demonstrates a growth trend as the size of the program
-increases.</t>
   </si>
   <si>
     <t>V Garousi, R Özkan, A Betin-Can</t>
@@ -547,27 +507,9 @@
     <t>Search-based algorithms</t>
   </si>
   <si>
-    <t>SIR (subset with 12 versions of 5 projects)</t>
-  </si>
-  <si>
-    <t>Different domains; between 600 and 15 test cases; LOC not provided;</t>
-  </si>
-  <si>
-    <t>Apparently none. They seed faults, and only seem to use fault coverage and execution time as objectives (!)</t>
-  </si>
-  <si>
-    <t>Number of faults detected and execution time</t>
-  </si>
-  <si>
-    <t>This is a low-quality work. Might have slipped through the QA</t>
-  </si>
-  <si>
     <t>Change-based; Design-based (UML)</t>
   </si>
   <si>
-    <t>Two-objectives (?) Not clear</t>
-  </si>
-  <si>
     <t>Two-objectives</t>
   </si>
   <si>
@@ -710,15 +652,6 @@
   </si>
   <si>
     <t>History-based, Requirements-based; Others</t>
-  </si>
-  <si>
-    <t>Heuristic-based (greedy)</t>
-  </si>
-  <si>
-    <t>8 projects used in prior studies</t>
-  </si>
-  <si>
-    <t>seeded faults, coverage</t>
   </si>
   <si>
     <t>changed requirements, method size and complexity</t>
@@ -1394,7 +1327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -1529,62 +1462,59 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="224" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="240" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2020</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2018</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="Z2" s="2" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AH2" s="2">
         <v>0</v>
       </c>
-      <c r="AI2" s="3" t="s">
-        <v>163</v>
-      </c>
     </row>
-    <row r="3" spans="1:35" ht="240" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="256" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>39</v>
@@ -1596,81 +1526,78 @@
         <v>41</v>
       </c>
       <c r="F3" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>42</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+    </row>
+    <row r="4" spans="1:35" ht="224" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>130</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2013</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="AB3" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AE4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH3" s="2">
+      <c r="AG4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:35" ht="256" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2021</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="3"/>
     </row>
     <row r="5" spans="1:35" ht="224" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>48</v>
@@ -1688,36 +1615,42 @@
         <v>51</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>177</v>
+        <v>150</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AH5" s="2">
         <v>0</v>
       </c>
+      <c r="AI5" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
-    <row r="6" spans="1:35" ht="224" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="240" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>52</v>
@@ -1729,48 +1662,42 @@
         <v>54</v>
       </c>
       <c r="F6" s="2">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="AH6" s="2">
         <v>0</v>
       </c>
-      <c r="AI6" s="2" t="s">
-        <v>183</v>
-      </c>
     </row>
-    <row r="7" spans="1:35" ht="240" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" ht="256" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>56</v>
@@ -1782,42 +1709,45 @@
         <v>58</v>
       </c>
       <c r="F7" s="2">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>59</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="AE7" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="AH7" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="256" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="335" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>60</v>
@@ -1829,45 +1759,45 @@
         <v>62</v>
       </c>
       <c r="F8" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="AH8" s="2">
         <v>1</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="335" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="208" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>64</v>
@@ -1879,45 +1809,45 @@
         <v>66</v>
       </c>
       <c r="F9" s="2">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="AB9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="AE9" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="AD9" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="AF9" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="AH9" s="2">
         <v>1</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="208" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>68</v>
@@ -1929,45 +1859,42 @@
         <v>70</v>
       </c>
       <c r="F10" s="2">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>189</v>
+        <v>150</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AH10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="2" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="208" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" ht="256" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>72</v>
@@ -1979,42 +1906,42 @@
         <v>74</v>
       </c>
       <c r="F11" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>75</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>208</v>
+        <v>170</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="AH11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="256" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>76</v>
@@ -2026,42 +1953,45 @@
         <v>78</v>
       </c>
       <c r="F12" s="2">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>79</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="AF12" s="2" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="AH12" s="2">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="256" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="192" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>80</v>
@@ -2073,42 +2003,48 @@
         <v>82</v>
       </c>
       <c r="F13" s="2">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>83</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="AH13" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="192" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>84</v>
@@ -2120,45 +2056,39 @@
         <v>86</v>
       </c>
       <c r="F14" s="2">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="AH14" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AI14" s="2" t="s">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="192" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" ht="240" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>88</v>
@@ -2170,48 +2100,42 @@
         <v>90</v>
       </c>
       <c r="F15" s="2">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>91</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="AC15" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="AD15" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="AD15" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="AE15" s="2" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="AH15" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI15" s="2" t="s">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="192" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="208" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>92</v>
@@ -2223,39 +2147,48 @@
         <v>94</v>
       </c>
       <c r="F16" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>95</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>233</v>
+        <v>221</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>232</v>
+        <v>223</v>
+      </c>
+      <c r="AF16" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>229</v>
+        <v>282</v>
       </c>
       <c r="AH16" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="240" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" ht="224" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>96</v>
@@ -2273,28 +2206,25 @@
         <v>99</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="AD17" s="2" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AH17" s="2">
         <v>0</v>
@@ -2302,7 +2232,7 @@
     </row>
     <row r="18" spans="1:35" ht="208" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>100</v>
@@ -2314,48 +2244,42 @@
         <v>102</v>
       </c>
       <c r="F18" s="2">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>103</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC18" s="2" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="AD18" s="2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>299</v>
+        <v>235</v>
       </c>
       <c r="AH18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI18" s="2" t="s">
-        <v>243</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="224" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" ht="256" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>104</v>
@@ -2367,39 +2291,45 @@
         <v>106</v>
       </c>
       <c r="F19" s="2">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>107</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AH19" s="2">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:35" ht="208" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -2411,42 +2341,42 @@
         <v>110</v>
       </c>
       <c r="F20" s="2">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>111</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="AD20" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="AE20" s="2" t="s">
-        <v>250</v>
+        <v>194</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>252</v>
+        <v>156</v>
       </c>
       <c r="AH20" s="2">
         <v>0</v>
       </c>
+      <c r="AI20" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
-    <row r="21" spans="1:35" ht="256" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" ht="320" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>112</v>
@@ -2458,45 +2388,45 @@
         <v>114</v>
       </c>
       <c r="F21" s="2">
-        <v>2014</v>
+        <v>2023</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>115</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="AD21" s="2" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AE21" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="AH21" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="208" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" ht="256" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>116</v>
@@ -2508,42 +2438,45 @@
         <v>118</v>
       </c>
       <c r="F22" s="2">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>119</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="AD22" s="2" t="s">
-        <v>208</v>
+        <v>170</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="AG22" s="2" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="AH22" s="2">
         <v>0</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="320" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" ht="192" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>120</v>
@@ -2555,45 +2488,48 @@
         <v>122</v>
       </c>
       <c r="F23" s="2">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>123</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>269</v>
+        <v>221</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="AD23" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AE23" s="2" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>267</v>
+        <v>172</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="AH23" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="256" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" ht="240" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>124</v>
@@ -2605,45 +2541,45 @@
         <v>126</v>
       </c>
       <c r="F24" s="2">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>127</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>189</v>
+        <v>263</v>
       </c>
       <c r="AD24" s="2" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
       <c r="AE24" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AG24" s="2" t="s">
-        <v>170</v>
+        <v>268</v>
       </c>
       <c r="AH24" s="2">
         <v>0</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="192" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" ht="304" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>128</v>
@@ -2655,48 +2591,45 @@
         <v>130</v>
       </c>
       <c r="F25" s="2">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>131</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC25" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AF25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="AD25" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AE25" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AF25" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AH25" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AI25" s="2" t="s">
-        <v>278</v>
-      </c>
     </row>
-    <row r="26" spans="1:35" ht="240" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" ht="160" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>132</v>
@@ -2708,45 +2641,45 @@
         <v>134</v>
       </c>
       <c r="F26" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>135</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="AD26" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AE26" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>283</v>
+        <v>245</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="AH26" s="2">
         <v>0</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="304" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" ht="208" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>136</v>
@@ -2758,284 +2691,184 @@
         <v>138</v>
       </c>
       <c r="F27" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>139</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AA27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB27" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD27" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AB27" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AD27" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="AE27" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AF27" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AG27" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="AH27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="2" t="s">
-        <v>291</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="160" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" ht="208" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>140</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2">
+        <v>2015</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F28" s="2">
-        <v>2022</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="Y28" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>233</v>
+        <v>221</v>
+      </c>
+      <c r="AC28" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>292</v>
+        <v>170</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="AH28" s="2">
         <v>0</v>
       </c>
-      <c r="AI28" s="2" t="s">
-        <v>294</v>
-      </c>
     </row>
-    <row r="29" spans="1:35" ht="208" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" ht="272" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2">
+        <v>2016</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F29" s="2">
-        <v>2020</v>
-      </c>
-      <c r="J29" s="2" t="s">
+      <c r="Y29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA29" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="AD29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE29" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AG29" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH29" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AI29" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" ht="256" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>161</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="Y29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z29" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA29" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="AB29" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC29" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="AD29" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="AE29" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="AG29" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="AH29" s="2">
+      <c r="D30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2022</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA30" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD30" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="AF30" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="AG30" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="AH30" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:35" ht="208" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>159</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F30" s="2">
-        <v>2015</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z30" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA30" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="AB30" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC30" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AD30" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE30" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="AF30" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AG30" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:35" ht="272" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>160</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F31" s="2">
-        <v>2016</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z31" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA31" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB31" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="AD31" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE31" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="AG31" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH31" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AI31" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="32" spans="1:35" ht="256" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>161</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F32" s="2">
-        <v>2022</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z32" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA32" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="AB32" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="AD32" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE32" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="AF32" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AG32" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="AH32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI32" s="2" t="s">
-        <v>310</v>
+      <c r="AI30" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -3045,6 +2878,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ab92c565-5003-4ac3-93a3-a3ce8796a3c0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B6889C2593FACB4192549183B8B19287" ma:contentTypeVersion="11" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="8f919e2780f892880bff7efb43d3db1d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ab92c565-5003-4ac3-93a3-a3ce8796a3c0" xmlns:ns3="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ca4d89da73e1329ebe7ff2e4ed471c6" ns2:_="" ns3:_="">
     <xsd:import namespace="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
@@ -3239,41 +3092,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ab92c565-5003-4ac3-93a3-a3ce8796a3c0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C59164E-2414-4B14-8C66-55EDA10EEEE8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC8D206C-82D8-4912-A7B5-092648EE9274}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
-    <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3296,9 +3118,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC8D206C-82D8-4912-A7B5-092648EE9274}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C59164E-2414-4B14-8C66-55EDA10EEEE8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
+    <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>